--- a/data/trans_dic/P44A$analisis-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P44A$analisis-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,46</t>
+          <t>0,0; 58,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 39,58</t>
+          <t>4,13; 38,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,45</t>
+          <t>0,0; 7,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 55,56</t>
+          <t>6,57; 53,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 14,21</t>
+          <t>1,51; 12,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,54</t>
+          <t>0,0; 27,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,7; 37,78</t>
+          <t>7,56; 37,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,24</t>
+          <t>1,37; 7,52</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 39,55</t>
+          <t>3,98; 37,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 67,42</t>
+          <t>8,74; 66,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,19; 48,86</t>
+          <t>23,52; 47,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,58; 40,64</t>
+          <t>4,59; 35,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,32</t>
+          <t>0,0; 77,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,82; 42,16</t>
+          <t>20,39; 42,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 30,24</t>
+          <t>6,79; 29,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 55,88</t>
+          <t>5,92; 53,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,91; 41,9</t>
+          <t>24,46; 41,33</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,23; 100,0</t>
+          <t>23,43; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,43; 75,75</t>
+          <t>34,04; 75,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 15,07</t>
+          <t>3,39; 15,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,99; 75,75</t>
+          <t>20,97; 74,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,49; 90,77</t>
+          <t>42,87; 89,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 7,31</t>
+          <t>0,7; 7,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,95; 80,92</t>
+          <t>34,31; 80,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,29; 75,84</t>
+          <t>44,8; 76,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 9,5</t>
+          <t>2,73; 9,51</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,99; 88,6</t>
+          <t>14,57; 78,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,03; 47,36</t>
+          <t>14,42; 49,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,41</t>
+          <t>1,08; 11,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,3</t>
+          <t>0,0; 47,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,94; 53,21</t>
+          <t>10,46; 52,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,18</t>
+          <t>0,9; 8,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,41; 51,12</t>
+          <t>14,66; 53,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,2; 44,35</t>
+          <t>16,88; 45,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 7,24</t>
+          <t>1,59; 6,95</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,3</t>
+          <t>0,0; 82,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1128,37 +1128,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 29,42</t>
+          <t>3,47; 30,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,62; 83,72</t>
+          <t>15,54; 83,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 77,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 25,69</t>
+          <t>2,69; 24,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,52; 68,02</t>
+          <t>16,68; 74,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,14; 85,85</t>
+          <t>13,91; 73,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,22; 22,23</t>
+          <t>4,64; 21,51</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,81; 76,26</t>
+          <t>9,77; 66,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,88</t>
+          <t>0,0; 49,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,18; 27,23</t>
+          <t>7,85; 27,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,76; 100,0</t>
+          <t>17,59; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,0; 76,95</t>
+          <t>11,63; 75,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,96; 19,02</t>
+          <t>4,11; 19,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,18; 73,3</t>
+          <t>20,43; 67,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,71; 55,99</t>
+          <t>10,34; 53,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,32; 19,82</t>
+          <t>7,28; 19,53</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>35,34; 92,72</t>
+          <t>33,87; 92,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,46; 69,74</t>
+          <t>36,85; 68,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,28; 30,26</t>
+          <t>15,47; 29,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,67; 74,91</t>
+          <t>28,4; 75,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,14; 52,9</t>
+          <t>15,24; 53,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,26; 13,23</t>
+          <t>5,48; 12,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,19; 76,17</t>
+          <t>39,4; 75,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,69; 57,42</t>
+          <t>31,89; 55,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,35; 20,26</t>
+          <t>11,7; 19,77</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,35; 51,57</t>
+          <t>12,74; 52,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,92; 48,97</t>
+          <t>11,0; 49,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,61; 92,13</t>
+          <t>6,34; 91,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,19; 57,44</t>
+          <t>7,31; 56,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,56</t>
+          <t>0,0; 46,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,34; 22,32</t>
+          <t>12,75; 22,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,34; 46,11</t>
+          <t>15,0; 45,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,26; 38,05</t>
+          <t>9,85; 38,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,59; 85,04</t>
+          <t>11,4; 85,73</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27,99; 47,61</t>
+          <t>27,93; 49,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29,1; 44,33</t>
+          <t>29,47; 44,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,88; 74,31</t>
+          <t>12,46; 74,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23,71; 41,96</t>
+          <t>22,85; 42,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,43; 44,45</t>
+          <t>24,92; 44,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,24; 13,41</t>
+          <t>9,3; 13,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,24; 41,87</t>
+          <t>27,99; 42,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29,93; 41,98</t>
+          <t>29,07; 41,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,88; 60,49</t>
+          <t>11,86; 62,71</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4136</t>
+          <t>0; 4096</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1060; 9249</t>
+          <t>965; 8880</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6201</t>
+          <t>0; 5609</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1890</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1014; 8770</t>
+          <t>1037; 8500</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>514; 4990</t>
+          <t>530; 4557</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6046</t>
+          <t>0; 4898</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3799; 14795</t>
+          <t>2961; 14653</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1395; 7855</t>
+          <t>1484; 8155</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>956; 9537</t>
+          <t>959; 8962</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>728; 6283</t>
+          <t>815; 6239</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14492; 30529</t>
+          <t>14698; 29486</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>935; 8296</t>
+          <t>937; 7147</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4410</t>
+          <t>0; 4404</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7832; 16660</t>
+          <t>8057; 16852</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2891; 13464</t>
+          <t>3022; 13095</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>995; 8395</t>
+          <t>889; 8093</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25404; 42735</t>
+          <t>24947; 42156</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2971; 9219</t>
+          <t>2160; 9219</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6982; 15823</t>
+          <t>7110; 15834</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1941; 8557</t>
+          <t>1926; 8604</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2661; 10084</t>
+          <t>2791; 9939</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8477; 18111</t>
+          <t>8554; 17951</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>387; 4078</t>
+          <t>393; 4158</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8325; 18231</t>
+          <t>7730; 18098</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18088; 30972</t>
+          <t>18297; 31276</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3121; 10698</t>
+          <t>3074; 10706</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1746; 9675</t>
+          <t>1591; 8618</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3651; 12326</t>
+          <t>3752; 12950</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>570; 5485</t>
+          <t>571; 5880</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5925</t>
+          <t>0; 6548</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2234; 10866</t>
+          <t>2136; 10733</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>546; 4828</t>
+          <t>532; 5099</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3298; 12577</t>
+          <t>3606; 13250</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7987; 20601</t>
+          <t>7841; 20992</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1913; 8086</t>
+          <t>1775; 7768</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5309</t>
+          <t>0; 5185</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2523,37 +2523,37 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>446; 3787</t>
+          <t>447; 3862</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1026; 5497</t>
+          <t>1020; 5491</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3989</t>
+          <t>0; 3097</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>371; 3580</t>
+          <t>375; 3357</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2125; 8750</t>
+          <t>2146; 9544</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>985; 5976</t>
+          <t>968; 5137</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1400; 5960</t>
+          <t>1243; 5767</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>908; 7053</t>
+          <t>904; 6120</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5493</t>
+          <t>0; 5093</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3187; 10601</t>
+          <t>3055; 10719</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1117; 6292</t>
+          <t>1107; 6292</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1032; 6622</t>
+          <t>1001; 6523</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1211; 5810</t>
+          <t>1255; 6031</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3136; 11391</t>
+          <t>3175; 10476</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2035; 10634</t>
+          <t>1963; 10144</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5084; 13770</t>
+          <t>5056; 13570</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5550; 14562</t>
+          <t>5319; 14578</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15104; 28120</t>
+          <t>14857; 27423</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16140; 31956</t>
+          <t>16338; 31524</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5281; 15410</t>
+          <t>5843; 15511</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4550; 14917</t>
+          <t>4298; 15177</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5999; 15092</t>
+          <t>6254; 14583</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14218; 27634</t>
+          <t>14293; 27337</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>22400; 39340</t>
+          <t>21848; 38182</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>24933; 44505</t>
+          <t>25705; 43445</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3323; 13877</t>
+          <t>3427; 14070</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3147; 12930</t>
+          <t>2906; 13116</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>24715; 344515</t>
+          <t>23721; 341719</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1082; 8642</t>
+          <t>1100; 8557</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 6272</t>
+          <t>0; 6257</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16060; 29038</t>
+          <t>16585; 29713</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6436; 19343</t>
+          <t>6295; 18938</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3692; 15174</t>
+          <t>3928; 15392</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>58445; 428657</t>
+          <t>57465; 432144</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>30607; 52072</t>
+          <t>30546; 53643</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>46469; 70793</t>
+          <t>47067; 71353</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100031; 577175</t>
+          <t>96806; 574811</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25357; 44873</t>
+          <t>24440; 45004</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>29533; 51612</t>
+          <t>28939; 51378</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44190; 64092</t>
+          <t>44454; 64367</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>61085; 90565</t>
+          <t>60545; 90964</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>82559; 115787</t>
+          <t>80188; 113112</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>149064; 759094</t>
+          <t>148812; 786892</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$analisis-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P44A$analisis-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,9</t>
+          <t>0,0; 48,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,13; 38,0</t>
+          <t>4,61; 37,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,65</t>
+          <t>0,0; 7,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 53,85</t>
+          <t>6,36; 55,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 12,97</t>
+          <t>1,39; 13,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,18</t>
+          <t>0,0; 23,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 37,42</t>
+          <t>7,91; 35,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,52</t>
+          <t>1,34; 6,88</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 37,17</t>
+          <t>4,14; 38,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,74; 66,95</t>
+          <t>8,49; 67,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,52; 47,19</t>
+          <t>23,07; 46,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 35,01</t>
+          <t>4,67; 35,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,2</t>
+          <t>0,0; 78,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,39; 42,64</t>
+          <t>21,2; 44,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,79; 29,41</t>
+          <t>6,95; 30,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 53,87</t>
+          <t>6,58; 54,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,46; 41,33</t>
+          <t>24,22; 41,57</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,43; 100,0</t>
+          <t>32,35; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,04; 75,81</t>
+          <t>31,69; 74,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 15,15</t>
+          <t>3,41; 16,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,97; 74,66</t>
+          <t>16,42; 74,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,87; 89,97</t>
+          <t>39,58; 89,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,46</t>
+          <t>1,11; 8,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,31; 80,33</t>
+          <t>35,99; 80,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,8; 76,58</t>
+          <t>44,69; 75,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 9,51</t>
+          <t>2,98; 10,09</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,57; 78,92</t>
+          <t>15,32; 78,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,42; 49,76</t>
+          <t>13,98; 48,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 11,16</t>
+          <t>0,95; 10,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,86</t>
+          <t>0,0; 40,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,46; 52,56</t>
+          <t>11,07; 53,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,64</t>
+          <t>0,81; 8,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,66; 53,86</t>
+          <t>13,45; 51,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,88; 45,2</t>
+          <t>17,52; 44,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,95</t>
+          <t>1,46; 7,15</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,33</t>
+          <t>0,0; 69,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1128,37 +1128,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 30,0</t>
+          <t>3,51; 29,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,54; 83,63</t>
+          <t>15,59; 83,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,65</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 24,09</t>
+          <t>2,65; 24,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,68; 74,19</t>
+          <t>16,6; 74,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,91; 73,79</t>
+          <t>14,24; 85,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 21,51</t>
+          <t>4,61; 20,98</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,77; 66,18</t>
+          <t>9,81; 65,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,03</t>
+          <t>0,0; 53,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,85; 27,53</t>
+          <t>8,38; 26,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,59; 100,0</t>
+          <t>17,58; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,63; 75,8</t>
+          <t>11,91; 76,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,11; 19,74</t>
+          <t>3,64; 19,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,43; 67,41</t>
+          <t>20,51; 73,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,34; 53,41</t>
+          <t>10,84; 52,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,28; 19,53</t>
+          <t>7,61; 19,73</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,87; 92,83</t>
+          <t>37,73; 92,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36,85; 68,01</t>
+          <t>36,65; 68,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,47; 29,85</t>
+          <t>15,09; 29,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28,4; 75,4</t>
+          <t>27,3; 77,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,24; 53,82</t>
+          <t>16,11; 54,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,78</t>
+          <t>6,15; 14,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,4; 75,36</t>
+          <t>39,42; 76,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>31,89; 55,73</t>
+          <t>31,83; 56,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,7; 19,77</t>
+          <t>11,37; 19,38</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,74; 52,29</t>
+          <t>12,64; 54,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,0; 49,67</t>
+          <t>12,87; 46,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,34; 91,38</t>
+          <t>4,87; 14,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,31; 56,87</t>
+          <t>7,08; 56,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,45</t>
+          <t>0,0; 45,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,75; 22,84</t>
+          <t>12,88; 22,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,0; 45,14</t>
+          <t>15,69; 45,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,85; 38,6</t>
+          <t>9,63; 37,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,4; 85,73</t>
+          <t>9,88; 16,49</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27,93; 49,05</t>
+          <t>28,55; 47,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29,47; 44,68</t>
+          <t>29,02; 44,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,46; 74,0</t>
+          <t>10,82; 16,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22,85; 42,08</t>
+          <t>22,73; 42,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24,92; 44,24</t>
+          <t>25,02; 43,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,3; 13,46</t>
+          <t>9,68; 13,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,99; 42,05</t>
+          <t>27,88; 41,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29,07; 41,01</t>
+          <t>29,82; 41,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,86; 62,71</t>
+          <t>10,92; 14,19</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3619</t>
         </is>
       </c>
     </row>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4096</t>
+          <t>0; 3353</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>965; 8880</t>
+          <t>1077; 8710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5609</t>
+          <t>0; 5717</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1881,27 +1881,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1037; 8500</t>
+          <t>1005; 8813</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>530; 4557</t>
+          <t>502; 4973</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4898</t>
+          <t>0; 4231</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2961; 14653</t>
+          <t>3099; 13863</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1484; 8155</t>
+          <t>1467; 7545</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>33508</t>
+          <t>35105</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>959; 8962</t>
+          <t>998; 9177</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>815; 6239</t>
+          <t>791; 6258</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14698; 29486</t>
+          <t>15006; 29969</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>937; 7147</t>
+          <t>953; 7315</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4404</t>
+          <t>0; 4485</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8057; 16852</t>
+          <t>8939; 18661</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3022; 13095</t>
+          <t>3095; 13398</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>889; 8093</t>
+          <t>988; 8204</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24947; 42156</t>
+          <t>25972; 44567</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6439</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2160; 9219</t>
+          <t>2982; 9219</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7110; 15834</t>
+          <t>6619; 15614</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1926; 8604</t>
+          <t>1900; 9074</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2791; 9939</t>
+          <t>2186; 9895</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8554; 17951</t>
+          <t>7898; 17891</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>393; 4158</t>
+          <t>637; 5008</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7730; 18098</t>
+          <t>8109; 18145</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18297; 31276</t>
+          <t>18250; 30770</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3074; 10706</t>
+          <t>3367; 11382</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4211</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1591; 8618</t>
+          <t>1673; 8578</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3752; 12950</t>
+          <t>3638; 12718</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>571; 5880</t>
+          <t>561; 6222</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6548</t>
+          <t>0; 5564</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2136; 10733</t>
+          <t>2260; 11002</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>532; 5099</t>
+          <t>516; 5161</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3606; 13250</t>
+          <t>3309; 12563</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7841; 20992</t>
+          <t>8137; 20745</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1775; 7768</t>
+          <t>1799; 8790</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3242</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5185</t>
+          <t>0; 4405</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2523,37 +2523,37 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>447; 3862</t>
+          <t>474; 3962</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1020; 5491</t>
+          <t>1024; 5491</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3097</t>
+          <t>0; 3989</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>375; 3357</t>
+          <t>391; 3565</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2146; 9544</t>
+          <t>2136; 9599</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>968; 5137</t>
+          <t>991; 5979</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1243; 5767</t>
+          <t>1304; 5930</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8801</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>904; 6120</t>
+          <t>908; 6079</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5093</t>
+          <t>0; 5510</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3055; 10719</t>
+          <t>3171; 10207</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1107; 6292</t>
+          <t>1106; 6292</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1001; 6523</t>
+          <t>1025; 6618</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1255; 6031</t>
+          <t>1131; 6066</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3175; 10476</t>
+          <t>3188; 11373</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1963; 10144</t>
+          <t>2059; 9988</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5056; 13570</t>
+          <t>5239; 13584</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23651</t>
+          <t>26256</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>12911</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>33566</t>
+          <t>39168</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5319; 14578</t>
+          <t>5925; 14579</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14857; 27423</t>
+          <t>14775; 27484</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16338; 31524</t>
+          <t>18338; 36384</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5843; 15511</t>
+          <t>5617; 16012</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4298; 15177</t>
+          <t>4543; 15318</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6254; 14583</t>
+          <t>8292; 19834</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14293; 27337</t>
+          <t>14301; 27641</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>21848; 38182</t>
+          <t>21809; 38554</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>25705; 43445</t>
+          <t>29141; 49676</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>254993</t>
+          <t>12390</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22105</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>277098</t>
+          <t>37640</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3427; 14070</t>
+          <t>3401; 14646</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2906; 13116</t>
+          <t>3398; 12367</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23721; 341719</t>
+          <t>7038; 20405</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1100; 8557</t>
+          <t>1064; 8560</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 6257</t>
+          <t>0; 6129</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16585; 29713</t>
+          <t>19141; 32819</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6295; 18938</t>
+          <t>6584; 19291</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3928; 15392</t>
+          <t>3840; 15114</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>57465; 432144</t>
+          <t>28945; 48324</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>315969</t>
+          <t>76147</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53924</t>
+          <t>62077</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>369892</t>
+          <t>138224</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>30546; 53643</t>
+          <t>31229; 52413</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>47067; 71353</t>
+          <t>46341; 70995</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96806; 574811</t>
+          <t>61756; 94022</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24440; 45004</t>
+          <t>24308; 45114</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>28939; 51378</t>
+          <t>29060; 50732</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44454; 64367</t>
+          <t>51114; 73872</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>60545; 90964</t>
+          <t>60319; 89254</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>80188; 113112</t>
+          <t>82236; 114733</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>148812; 786892</t>
+          <t>120008; 155990</t>
         </is>
       </c>
     </row>
